--- a/Calendário 2DS-MB.xlsx
+++ b/Calendário 2DS-MB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desktop\Desktop\SENAI\02 - Disciplinas\03 - PWBE\02 - PWBE 2DS\21 - Calendário\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3C86CC-2447-4D83-BE5D-4B1E84776512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8D9729-FBE2-4D21-B5DF-DFCF7F54437F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E39C29BC-6674-47EC-9BAE-59D878940E0F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
   <si>
     <t>MAIO</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t xml:space="preserve">Colocar o professor como colaborador do repositório com o email lindomarbatistao@gmail.com  </t>
+  </si>
+  <si>
+    <t>A pergunta Oral pode ocorrer nos dias 29/05 ou 03/06 onde é o aluno que deve escolher</t>
   </si>
 </sst>
 </file>
@@ -115,7 +118,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,8 +173,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -194,18 +203,77 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -215,8 +283,44 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,26 +648,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="J2" s="4" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="J2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="7" t="s">
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -612,7 +716,7 @@
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>17</v>
       </c>
       <c r="C4" s="2">
@@ -627,19 +731,19 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="J4" s="5"/>
+      <c r="J4" s="4"/>
       <c r="K4" s="2">
         <f>J4+1</f>
         <v>1</v>
@@ -648,29 +752,29 @@
         <f t="shared" ref="L4:P4" si="1">K4+1</f>
         <v>2</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="7">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="9">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="9">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="4">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="R4" s="8"/>
+      <c r="R4" s="7"/>
       <c r="S4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <f>H4+1</f>
         <v>24</v>
       </c>
@@ -686,49 +790,49 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <f>P4+1</f>
         <v>7</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="8">
         <f>J5+1</f>
         <v>8</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="8">
         <f t="shared" ref="L5:P5" si="3">K5+1</f>
         <v>9</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="8">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="12">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="8">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="P5" s="5">
+      <c r="P5" s="4">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <f>H5+1</f>
         <v>31</v>
       </c>
@@ -737,9 +841,9 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="5"/>
-      <c r="J6" s="5">
-        <f t="shared" ref="J6:J9" si="4">P5+1</f>
+      <c r="H6" s="4"/>
+      <c r="J6" s="4">
+        <f t="shared" ref="J6:J8" si="4">P5+1</f>
         <v>14</v>
       </c>
       <c r="K6" s="2">
@@ -754,32 +858,32 @@
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="N6" s="12">
+      <c r="N6" s="11">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="10">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P6" s="4">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="R6" s="9"/>
+      <c r="R6" s="8"/>
       <c r="S6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B7" s="5"/>
+      <c r="B7" s="4"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="5"/>
-      <c r="J7" s="5">
+      <c r="H7" s="4"/>
+      <c r="J7" s="4">
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
@@ -787,74 +891,74 @@
         <f t="shared" ref="K7:P7" si="6">J7+1</f>
         <v>22</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="4">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="4">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="4">
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="4">
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="P7" s="5">
+      <c r="P7" s="4">
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B8" s="5"/>
+      <c r="B8" s="4"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="5"/>
-      <c r="J8" s="5">
+      <c r="H8" s="4"/>
+      <c r="J8" s="4">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="K8" s="5">
-        <f t="shared" ref="K8:P8" si="7">J8+1</f>
+      <c r="K8" s="4">
+        <f t="shared" ref="K8:L8" si="7">J8+1</f>
         <v>29</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="4">
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="R8" s="10"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="R8" s="9"/>
       <c r="S8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B9" s="5"/>
+      <c r="B9" s="4"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
+      <c r="H9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="R10" s="11">
+      <c r="R10" s="10">
         <v>19</v>
       </c>
       <c r="S10" t="s">
@@ -865,63 +969,63 @@
       <c r="B11" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="16"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="R12" s="12">
+      <c r="B12" s="17"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="19"/>
+      <c r="R12" s="11">
         <v>18</v>
       </c>
       <c r="S12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-    </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="R14" s="13">
+      <c r="B14" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="22"/>
+      <c r="R14" s="12">
         <v>11</v>
       </c>
       <c r="S14" t="s">
@@ -929,6 +1033,21 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="25"/>
       <c r="S15" t="s">
         <v>13</v>
       </c>
@@ -939,10 +1058,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="J2:P2"/>
-    <mergeCell ref="B11:P13"/>
+    <mergeCell ref="B11:P12"/>
+    <mergeCell ref="B14:P15"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Calendário 2DS-MB.xlsx
+++ b/Calendário 2DS-MB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desktop\Desktop\SENAI\02 - Disciplinas\03 - PWBE\02 - PWBE 2DS\21 - Calendário\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\27120642839\Documents\fim_semestre_2026_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8D9729-FBE2-4D21-B5DF-DFCF7F54437F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4891B315-9898-4474-86BD-5D94377FB547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E39C29BC-6674-47EC-9BAE-59D878940E0F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E39C29BC-6674-47EC-9BAE-59D878940E0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -87,7 +84,7 @@
     <t xml:space="preserve">Colocar o professor como colaborador do repositório com o email lindomarbatistao@gmail.com  </t>
   </si>
   <si>
-    <t>A pergunta Oral pode ocorrer nos dias 29/05 ou 03/06 onde é o aluno que deve escolher</t>
+    <t>A pergunta Oral pode ocorrerá dia 03/06.</t>
   </si>
 </sst>
 </file>
@@ -269,14 +266,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -345,9 +340,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -385,7 +380,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -491,7 +486,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -633,7 +628,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -648,26 +643,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="J2" s="13" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="J2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="6" t="s">
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="R2" s="4"/>
+      <c r="S2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -731,11 +726,11 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -752,15 +747,15 @@
         <f t="shared" ref="L4:P4" si="1">K4+1</f>
         <v>2</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="5">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N4" s="9">
+      <c r="N4" s="7">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="O4" s="9">
+      <c r="O4" s="7">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -768,7 +763,7 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="R4" s="7"/>
+      <c r="R4" s="5"/>
       <c r="S4" t="s">
         <v>6</v>
       </c>
@@ -790,11 +785,11 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
@@ -806,23 +801,23 @@
         <f>P4+1</f>
         <v>7</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="6">
         <f>J5+1</f>
         <v>8</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="6">
         <f t="shared" ref="L5:P5" si="3">K5+1</f>
         <v>9</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="6">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N5" s="12">
+      <c r="N5" s="10">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="6">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
@@ -858,11 +853,11 @@
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="9">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="8">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
@@ -870,7 +865,7 @@
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="R6" s="8"/>
+      <c r="R6" s="6"/>
       <c r="S6" t="s">
         <v>7</v>
       </c>
@@ -936,7 +931,7 @@
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
-      <c r="R8" s="9"/>
+      <c r="R8" s="7"/>
       <c r="S8" t="s">
         <v>8</v>
       </c>
@@ -958,7 +953,7 @@
       <c r="P9" s="4"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="R10" s="10">
+      <c r="R10" s="8">
         <v>19</v>
       </c>
       <c r="S10" t="s">
@@ -966,41 +961,41 @@
       </c>
     </row>
     <row r="11" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="16"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="14"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="19"/>
-      <c r="R12" s="11">
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="17"/>
+      <c r="R12" s="9">
         <v>18</v>
       </c>
       <c r="S12" t="s">
@@ -1008,24 +1003,24 @@
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="22"/>
-      <c r="R14" s="12">
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="20"/>
+      <c r="R14" s="10">
         <v>11</v>
       </c>
       <c r="S14" t="s">
@@ -1033,21 +1028,21 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B15" s="23"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="25"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="23"/>
       <c r="S15" t="s">
         <v>13</v>
       </c>
